--- a/output/graficos_regionales/plot_regional_serie_i_ingr_m_2023_coquimbo.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_m_2023_coquimbo.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:36</t>
+    <t xml:space="preserve">2026-10-05 01:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -726,7 +726,7 @@
         <v>760829.5</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>804762.62</v>
+        <v>804762.63</v>
       </c>
     </row>
     <row r="5">
@@ -737,7 +737,7 @@
         <v>760197.19</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>799364.12</v>
+        <v>799364.13</v>
       </c>
     </row>
     <row r="6">
@@ -767,7 +767,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>764468.12</v>
+        <v>764468.13</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>805474.38</v>
@@ -800,7 +800,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>772234.12</v>
+        <v>772234.13</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>815571.81</v>
@@ -836,7 +836,7 @@
         <v>792894.94</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>826816.62</v>
+        <v>826816.63</v>
       </c>
     </row>
     <row r="15">
@@ -855,7 +855,7 @@
         <v>17</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>794210.12</v>
+        <v>794210.13</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>844828.88</v>
@@ -866,7 +866,7 @@
         <v>18</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>805550.62</v>
+        <v>805550.63</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>845150.88</v>
@@ -913,7 +913,7 @@
         <v>803207.94</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>849932.62</v>
+        <v>849932.63</v>
       </c>
     </row>
     <row r="22">
@@ -954,7 +954,7 @@
         <v>26</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>887454.62</v>
+        <v>887454.63</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>928044.19</v>
@@ -998,10 +998,10 @@
         <v>30</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>848970.12</v>
+        <v>848970.13</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>885489.12</v>
+        <v>885489.13</v>
       </c>
     </row>
     <row r="30">
@@ -1012,7 +1012,7 @@
         <v>841522.81</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>873830.12</v>
+        <v>873830.13</v>
       </c>
     </row>
     <row r="31">
@@ -1031,7 +1031,7 @@
         <v>33</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>848690.62</v>
+        <v>848690.63</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>883003.31</v>
@@ -1075,7 +1075,7 @@
         <v>37</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>877055.62</v>
+        <v>877055.63</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>900212.25</v>
@@ -1152,7 +1152,7 @@
         <v>44</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>915386.62</v>
+        <v>915386.63</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>943650.75</v>
@@ -1166,7 +1166,7 @@
         <v>927731.44</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>953641.12</v>
+        <v>953641.13</v>
       </c>
     </row>
     <row r="45">
@@ -1240,7 +1240,7 @@
         <v>52</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>958084.12</v>
+        <v>958084.13</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>984727.69</v>
@@ -1287,7 +1287,7 @@
         <v>1016705.81</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>1048559.62</v>
+        <v>1048559.63</v>
       </c>
     </row>
     <row r="56">
@@ -1298,7 +1298,7 @@
         <v>1041841.69</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1059287.62</v>
+        <v>1059287.63</v>
       </c>
     </row>
     <row r="57">
@@ -1328,7 +1328,7 @@
         <v>60</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>1067698.12</v>
+        <v>1067698.13</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>1086115.25</v>
@@ -1342,7 +1342,7 @@
         <v>1080522.25</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>1093564.62</v>
+        <v>1093564.63</v>
       </c>
     </row>
     <row r="61">
@@ -1350,7 +1350,7 @@
         <v>62</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>1161449.62</v>
+        <v>1161449.63</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>1183065.88</v>
@@ -1364,7 +1364,7 @@
         <v>1130567.25</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>1145616.62</v>
+        <v>1145616.63</v>
       </c>
     </row>
     <row r="63">
@@ -1394,7 +1394,7 @@
         <v>66</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>1157206.62</v>
+        <v>1157206.63</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>1168289.25</v>
@@ -1419,7 +1419,7 @@
         <v>1151874.75</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>1184430.62</v>
+        <v>1184430.63</v>
       </c>
     </row>
     <row r="68">
@@ -1449,7 +1449,7 @@
         <v>71</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>1226183.12</v>
+        <v>1226183.13</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>1246393.5</v>
@@ -1504,7 +1504,7 @@
         <v>76</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>1183242.62</v>
+        <v>1183242.63</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>1214165.25</v>
@@ -1518,7 +1518,7 @@
         <v>1211813.5</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>1240434.12</v>
+        <v>1240434.13</v>
       </c>
     </row>
     <row r="77">
@@ -1537,7 +1537,7 @@
         <v>79</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>1218199.12</v>
+        <v>1218199.13</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>1242222.38</v>
@@ -1548,10 +1548,10 @@
         <v>80</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>1220346.62</v>
+        <v>1220346.63</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>1253268.12</v>
+        <v>1253268.13</v>
       </c>
     </row>
     <row r="80">
@@ -1562,7 +1562,7 @@
         <v>1264846.38</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>1274861.62</v>
+        <v>1274861.63</v>
       </c>
     </row>
     <row r="81">
@@ -1584,7 +1584,7 @@
         <v>1311071.88</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>1327655.12</v>
+        <v>1327655.13</v>
       </c>
     </row>
     <row r="83">
